--- a/data/vendor_template_poc.xlsx
+++ b/data/vendor_template_poc.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="비정상평가" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이슈로그'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이슈로그'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'런기록'!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'비정상평가'!$A$1:$D$1</definedName>
   </definedNames>
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -741,8 +741,10 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -778,10 +780,20 @@
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
+          <t>종결일</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>무발생검증</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
           <t>상세</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>사진(파일명)</t>
         </is>
@@ -820,12 +832,18 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
           <t>픽업 좌표 인식 실패 — 노출 보정으로 해결</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>← 예시. 원인분류: 컨셉 리스크/설계/구현(SW)/시험환경</t>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>← 예시. 원인분류: 컨셉 리스크/설계/구현(SW)/시험환경 · 종결일·무발생검증(n/목표Cy)은 선택</t>
         </is>
       </c>
     </row>
@@ -852,7 +870,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>조치중</t>
+          <t>검증중</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -860,12 +878,18 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>토크 상한 이탈 — 프로파일 재설계 진행</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>41/50Cy</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>토크 상한 이탈 — 프로파일 재설계 후 무발생 감시</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="n"/>
@@ -876,6 +900,8 @@
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="8" t="n"/>
@@ -886,6 +912,8 @@
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
+      <c r="J5" s="8" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -896,6 +924,8 @@
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
       <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="n"/>
@@ -906,6 +936,8 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
+      <c r="J7" s="8" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -916,6 +948,8 @@
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
       <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="n"/>
@@ -926,6 +960,8 @@
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="7" t="n"/>
@@ -936,6 +972,8 @@
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
       <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="n"/>
@@ -946,6 +984,8 @@
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
+      <c r="J11" s="8" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="7" t="n"/>
@@ -956,6 +996,8 @@
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
       <c r="H12" s="7" t="n"/>
+      <c r="I12" s="7" t="n"/>
+      <c r="J12" s="7" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="n"/>
@@ -966,6 +1008,8 @@
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
+      <c r="J13" s="8" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="7" t="n"/>
@@ -976,6 +1020,8 @@
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
       <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="n"/>
@@ -986,6 +1032,8 @@
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
+      <c r="J15" s="8" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="7" t="n"/>
@@ -996,6 +1044,8 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="7" t="n"/>
       <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="n"/>
@@ -1006,6 +1056,8 @@
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
+      <c r="J17" s="8" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="7" t="n"/>
@@ -1016,6 +1068,8 @@
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="7" t="n"/>
       <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="n"/>
@@ -1026,6 +1080,8 @@
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="7" t="n"/>
@@ -1036,6 +1092,8 @@
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="n"/>
@@ -1046,9 +1104,11 @@
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
+      <c r="J21" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
